--- a/rules/CORE-001064/negative/01/data/unit-test-coreid-FB2305-negative.xlsx
+++ b/rules/CORE-001064/negative/01/data/unit-test-coreid-FB2305-negative.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-001064\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41358EE-4676-4A6C-A890-5C2DD425C43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49A39D8-64B3-4C81-904C-3FBA01444918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="349" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="349" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="212">
   <si>
     <t>Product</t>
   </si>
@@ -168,91 +168,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>ACTSUB</t>
-  </si>
-  <si>
-    <t>Actual Number of Subjects</t>
-  </si>
-  <si>
-    <t>341</t>
-  </si>
-  <si>
-    <t>ADAPT</t>
-  </si>
-  <si>
-    <t>Adaptive Design</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
-    <t>C49487</t>
-  </si>
-  <si>
     <t>CDISC</t>
   </si>
   <si>
     <t>2015-03-27</t>
   </si>
   <si>
-    <t>ADDON</t>
-  </si>
-  <si>
-    <t>Added on to Existing Treatments</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
-    <t>C49488</t>
-  </si>
-  <si>
-    <t>AGEMAX</t>
-  </si>
-  <si>
-    <t>Planned Maximum Age of Subjects</t>
-  </si>
-  <si>
-    <t>PINF</t>
-  </si>
-  <si>
-    <t>ISO 21090</t>
-  </si>
-  <si>
-    <t>AGEMIN</t>
-  </si>
-  <si>
-    <t>Planned Minimum Age of Subjects</t>
-  </si>
-  <si>
-    <t>P18Y</t>
-  </si>
-  <si>
-    <t>ISO 8601</t>
-  </si>
-  <si>
     <t>CARX</t>
-  </si>
-  <si>
-    <t>CURTRT</t>
-  </si>
-  <si>
-    <t>Current Therapy or Treatment</t>
-  </si>
-  <si>
-    <t>72X6E3J5AR</t>
-  </si>
-  <si>
-    <t>UNII</t>
-  </si>
-  <si>
-    <t>2021-12-13</t>
-  </si>
-  <si>
-    <t>DEX</t>
-  </si>
-  <si>
-    <t>7S5I7G3JQL</t>
   </si>
   <si>
     <t>DOSE</t>
@@ -741,9 +669,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -762,14 +690,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -855,7 +775,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -869,9 +789,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -914,13 +831,7 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1335,16 +1246,16 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="D2">
         <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="F2" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1355,16 +1266,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1375,16 +1286,16 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1394,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="22" customWidth="1"/>
@@ -1540,7 +1451,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>44</v>
       </c>
@@ -1548,17 +1459,19 @@
         <v>45</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="6"/>
+        <v>43</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="E5" s="6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
@@ -1576,27 +1489,27 @@
         <v>46</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>52</v>
+      <c r="E6" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>44</v>
       </c>
@@ -1606,319 +1519,87 @@
       <c r="C7" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="J7" s="24" t="s">
-        <v>54</v>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="6" t="s">
+        <v>46</v>
+      </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6" t="s">
-        <v>62</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="6"/>
       <c r="I8" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-    </row>
-    <row r="9" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="6"/>
+      <c r="C9" s="6" t="s">
+        <v>46</v>
+      </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-    </row>
-    <row r="10" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J9" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K9" s="6" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="75" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-    </row>
-    <row r="13" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-    </row>
-    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1936,310 +1617,310 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="W1" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="X1" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G2" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H2" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I2" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J2" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K2" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="L2" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="M2" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N2" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O2" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P2" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q2" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R2" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S2" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="T2" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="U2" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="V2" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="W2" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="W1" s="27" t="s">
+      <c r="X2" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="Y2" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="Y1" s="9" t="s">
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="T3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="V3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="W3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y3" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <v>12</v>
+      </c>
+      <c r="B4" s="10">
+        <v>2</v>
+      </c>
+      <c r="C4" s="11">
+        <v>20</v>
+      </c>
+      <c r="D4" s="11">
+        <v>12</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="T2" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="U2" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="W2" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="11" t="s">
+      <c r="F4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="L4" s="10">
+        <v>1</v>
+      </c>
+      <c r="M4" s="10">
+        <v>3</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="O4" s="10">
+        <v>8</v>
+      </c>
+      <c r="P4" s="11">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="10">
+        <v>5</v>
+      </c>
+      <c r="R4" s="10">
+        <v>1</v>
+      </c>
+      <c r="S4" s="10">
         <v>41</v>
       </c>
-      <c r="P3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="R3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="S3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="T3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="U3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="W3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="X3" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y3" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
-        <v>12</v>
-      </c>
-      <c r="B4" s="11">
-        <v>2</v>
-      </c>
-      <c r="C4" s="12">
-        <v>20</v>
-      </c>
-      <c r="D4" s="12">
-        <v>12</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="L4" s="11">
-        <v>1</v>
-      </c>
-      <c r="M4" s="11">
-        <v>3</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="O4" s="11">
+      <c r="T4" s="10">
+        <v>22</v>
+      </c>
+      <c r="U4" s="10">
         <v>8</v>
       </c>
-      <c r="P4" s="12">
-        <v>5</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>5</v>
-      </c>
-      <c r="R4" s="11">
-        <v>1</v>
-      </c>
-      <c r="S4" s="11">
-        <v>41</v>
-      </c>
-      <c r="T4" s="11">
-        <v>22</v>
-      </c>
-      <c r="U4" s="11">
+      <c r="V4" s="10">
+        <v>28</v>
+      </c>
+      <c r="W4" s="10">
         <v>8</v>
       </c>
-      <c r="V4" s="11">
+      <c r="X4" s="10">
         <v>28</v>
       </c>
-      <c r="W4" s="11">
-        <v>8</v>
-      </c>
-      <c r="X4" s="11">
-        <v>28</v>
-      </c>
-      <c r="Y4" s="11">
+      <c r="Y4" s="10">
         <v>3</v>
       </c>
     </row>
@@ -2248,72 +1929,72 @@
         <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="O5" s="15">
+        <v>121</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="L5" s="12"/>
+      <c r="M5" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="O5" s="14">
         <v>78</v>
       </c>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="R5" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="S5" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="T5" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="U5" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="V5" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="W5" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="X5" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y5" s="14" t="s">
-        <v>160</v>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="S5" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="T5" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="U5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="V5" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="W5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="X5" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y5" s="13" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -2321,74 +2002,74 @@
         <v>44</v>
       </c>
       <c r="B6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="O6" s="14">
+        <v>70</v>
+      </c>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="S6" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="T6" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="M6" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="N6" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="O6" s="15">
-        <v>70</v>
-      </c>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="R6" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="S6" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="T6" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="U6" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="V6" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="W6" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="X6" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y6" s="14" t="s">
-        <v>170</v>
+      <c r="U6" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="V6" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="W6" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="X6" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y6" s="13" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -2396,74 +2077,74 @@
         <v>44</v>
       </c>
       <c r="B7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="O7" s="14">
+        <v>71</v>
+      </c>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="R7" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="S7" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="T7" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="M7" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="N7" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="O7" s="15">
-        <v>71</v>
-      </c>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="R7" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="S7" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="T7" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="U7" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="V7" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="W7" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="X7" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y7" s="14" t="s">
-        <v>176</v>
+      <c r="U7" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="V7" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="W7" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="X7" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y7" s="13" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -2471,74 +2152,74 @@
         <v>44</v>
       </c>
       <c r="B8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="O8" s="14">
+        <v>71</v>
+      </c>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="R8" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="S8" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="T8" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="M8" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="N8" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="O8" s="15">
-        <v>71</v>
-      </c>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="R8" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="S8" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="T8" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="U8" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="V8" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="W8" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="X8" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y8" s="14" t="s">
-        <v>176</v>
+      <c r="U8" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="V8" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="W8" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="X8" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y8" s="13" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -2546,74 +2227,74 @@
         <v>44</v>
       </c>
       <c r="B9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="O9" s="14">
+        <v>71</v>
+      </c>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="R9" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="S9" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="T9" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="M9" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="N9" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="O9" s="15">
-        <v>71</v>
-      </c>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="R9" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="S9" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="T9" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="U9" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="V9" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="W9" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="X9" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="Y9" s="14" t="s">
-        <v>176</v>
+      <c r="U9" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="V9" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="W9" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="X9" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y9" s="13" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -2621,74 +2302,74 @@
         <v>44</v>
       </c>
       <c r="B10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="O10" s="14">
+        <v>71</v>
+      </c>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="R10" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="S10" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="T10" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="E10" s="14" t="s">
+      <c r="U10" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="V10" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="F10" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="G10" s="14" t="s">
+      <c r="W10" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="X10" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="H10" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="M10" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="N10" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="O10" s="15">
-        <v>71</v>
-      </c>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="R10" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="S10" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="T10" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="U10" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="V10" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="W10" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="X10" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="Y10" s="14" t="s">
-        <v>176</v>
+      <c r="Y10" s="13" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -2696,74 +2377,74 @@
         <v>44</v>
       </c>
       <c r="B11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="O11" s="14">
+        <v>71</v>
+      </c>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="R11" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="S11" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="T11" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="J11" s="14" t="s">
+      <c r="U11" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="V11" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="W11" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="K11" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="M11" s="14" t="s">
+      <c r="X11" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="N11" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="O11" s="15">
-        <v>71</v>
-      </c>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="R11" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="S11" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="T11" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="U11" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="V11" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="W11" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="X11" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="Y11" s="14" t="s">
-        <v>176</v>
+      <c r="Y11" s="13" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -2782,59 +2463,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="I1" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>199</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="M1" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="N1" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="O1" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="P1" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q1" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="R1" s="17" t="s">
-        <v>206</v>
+      <c r="C1" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="M1" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="N1" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="R1" s="16" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="75" x14ac:dyDescent="0.25">
@@ -2845,52 +2526,52 @@
         <v>30</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -2957,7 +2638,7 @@
         <v>43</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="D4" s="4">
         <v>8</v>
@@ -2993,10 +2674,10 @@
         <v>50</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="Q4" s="4">
         <v>8</v>
@@ -3010,45 +2691,45 @@
         <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>219</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>146</v>
+        <v>195</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="F5" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
-      <c r="I5" s="19" t="s">
-        <v>222</v>
+      <c r="I5" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="J5" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="K5" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="L5" t="s">
-        <v>225</v>
-      </c>
-      <c r="M5" s="20">
+        <v>201</v>
+      </c>
+      <c r="M5" s="19">
         <v>0.1</v>
       </c>
-      <c r="N5" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="O5" s="22">
+      <c r="N5" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="O5" s="21">
         <v>40557</v>
       </c>
-      <c r="P5" s="22">
+      <c r="P5" s="21">
         <v>40571</v>
       </c>
       <c r="Q5">
@@ -3063,45 +2744,45 @@
         <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>146</v>
+        <v>195</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="F6" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="G6">
         <v>3</v>
       </c>
-      <c r="I6" s="19" t="s">
-        <v>222</v>
+      <c r="I6" s="18" t="s">
+        <v>198</v>
       </c>
       <c r="J6" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="K6" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="L6" t="s">
-        <v>225</v>
-      </c>
-      <c r="M6" s="20">
+        <v>201</v>
+      </c>
+      <c r="M6" s="19">
         <v>0.1</v>
       </c>
-      <c r="N6" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="O6" s="22">
+      <c r="N6" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="O6" s="21">
         <v>40557</v>
       </c>
-      <c r="P6" s="22">
+      <c r="P6" s="21">
         <v>40571</v>
       </c>
       <c r="Q6">
@@ -3116,39 +2797,39 @@
         <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>219</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>161</v>
+        <v>195</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>137</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="F7" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="G7">
         <v>500</v>
       </c>
       <c r="I7" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="J7" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="K7" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="L7" t="s">
-        <v>233</v>
-      </c>
-      <c r="O7" s="22">
+        <v>209</v>
+      </c>
+      <c r="O7" s="21">
         <v>40557</v>
       </c>
-      <c r="P7" s="22">
+      <c r="P7" s="21">
         <v>40566</v>
       </c>
       <c r="Q7">
@@ -3163,39 +2844,39 @@
         <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>161</v>
+        <v>195</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>137</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="F8" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="G8">
         <v>500</v>
       </c>
       <c r="I8" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="J8" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="K8" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="L8" t="s">
-        <v>233</v>
-      </c>
-      <c r="O8" s="22">
+        <v>209</v>
+      </c>
+      <c r="O8" s="21">
         <v>40568</v>
       </c>
-      <c r="P8" s="22">
+      <c r="P8" s="21">
         <v>40571</v>
       </c>
       <c r="Q8">
@@ -3210,37 +2891,37 @@
         <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>171</v>
+        <v>195</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="G9">
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="J9" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="K9" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="L9" t="s">
-        <v>233</v>
-      </c>
-      <c r="O9" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="P9" s="22" t="s">
-        <v>164</v>
+        <v>209</v>
+      </c>
+      <c r="O9" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="P9" s="21" t="s">
+        <v>140</v>
       </c>
       <c r="Q9">
         <v>12</v>
